--- a/ae_master.xlsx
+++ b/ae_master.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Matrix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alerts by Site" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hardware Failure Map" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules vs Alerts" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device Type Breakdown" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Site Master" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Portfolio Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Risk Matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Alerts by Site" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Hardware Failure Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Rules vs Alerts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Device Type Breakdown" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Full Site Master" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2144,11 +2144,7 @@
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr"/>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D32" s="10" t="inlineStr"/>
       <c r="E32" s="10" t="inlineStr"/>
       <c r="F32" s="10" t="inlineStr"/>
       <c r="G32" s="10" t="n">
@@ -2190,11 +2186,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr"/>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D33" s="12" t="inlineStr"/>
       <c r="E33" s="12" t="inlineStr"/>
       <c r="F33" s="12" t="inlineStr"/>
       <c r="G33" s="12" t="n">
@@ -2236,11 +2228,7 @@
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr"/>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D34" s="10" t="inlineStr"/>
       <c r="E34" s="10" t="inlineStr"/>
       <c r="F34" s="10" t="inlineStr"/>
       <c r="G34" s="10" t="n">
@@ -2280,11 +2268,7 @@
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr"/>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D35" s="12" t="inlineStr"/>
       <c r="E35" s="12" t="inlineStr"/>
       <c r="F35" s="12" t="inlineStr"/>
       <c r="G35" s="12" t="n">
@@ -2326,11 +2310,7 @@
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr"/>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D36" s="10" t="inlineStr"/>
       <c r="E36" s="10" t="inlineStr"/>
       <c r="F36" s="10" t="inlineStr"/>
       <c r="G36" s="10" t="n">
@@ -3513,11 +3493,7 @@
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr"/>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="C32" s="10" t="inlineStr"/>
       <c r="D32" s="10" t="inlineStr"/>
       <c r="E32" s="10" t="n">
         <v>2</v>
@@ -3545,11 +3521,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr"/>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="C33" s="12" t="inlineStr"/>
       <c r="D33" s="12" t="inlineStr"/>
       <c r="E33" s="12" t="n">
         <v>5</v>
@@ -3577,11 +3549,7 @@
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr"/>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="C34" s="10" t="inlineStr"/>
       <c r="D34" s="10" t="inlineStr"/>
       <c r="E34" s="10" t="n">
         <v>6</v>
@@ -3609,11 +3577,7 @@
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr"/>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="C35" s="12" t="inlineStr"/>
       <c r="D35" s="12" t="inlineStr"/>
       <c r="E35" s="12" t="n">
         <v>0</v>
@@ -3641,11 +3605,7 @@
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr"/>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="C36" s="10" t="inlineStr"/>
       <c r="D36" s="10" t="inlineStr"/>
       <c r="E36" s="10" t="n">
         <v>2</v>
@@ -9135,7 +9095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9150,7 +9110,8 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9211,10 +9172,15 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>current_kw</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>risk_score</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>risk_tier</t>
         </is>
@@ -9267,9 +9233,12 @@
         <v>55</v>
       </c>
       <c r="L2" s="2" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -9322,9 +9291,12 @@
         <v>57</v>
       </c>
       <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -9377,9 +9349,12 @@
         <v>32</v>
       </c>
       <c r="L4" s="2" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -9432,9 +9407,12 @@
         <v>59</v>
       </c>
       <c r="L5" s="2" t="n">
+        <v>-8.49</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -9487,9 +9465,12 @@
         <v>52</v>
       </c>
       <c r="L6" s="2" t="n">
+        <v>-11.97</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -9542,9 +9523,12 @@
         <v>99</v>
       </c>
       <c r="L7" s="2" t="n">
+        <v>-11.93</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -9597,9 +9581,12 @@
         <v>26</v>
       </c>
       <c r="L8" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -9652,9 +9639,12 @@
         <v>103</v>
       </c>
       <c r="L9" s="2" t="n">
+        <v>-14.72</v>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -9707,9 +9697,12 @@
         <v>56</v>
       </c>
       <c r="L10" s="2" t="n">
+        <v>-7.22</v>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -9762,9 +9755,12 @@
         <v>32</v>
       </c>
       <c r="L11" s="2" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="M11" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -9817,9 +9813,12 @@
         <v>91</v>
       </c>
       <c r="L12" s="2" t="n">
+        <v>-12.76</v>
+      </c>
+      <c r="M12" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -9872,9 +9871,12 @@
         <v>41</v>
       </c>
       <c r="L13" s="2" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="M13" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -9927,9 +9929,12 @@
         <v>58</v>
       </c>
       <c r="L14" s="2" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="M14" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -9982,9 +9987,12 @@
         <v>56</v>
       </c>
       <c r="L15" s="2" t="n">
+        <v>-7.93</v>
+      </c>
+      <c r="M15" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -10037,9 +10045,12 @@
         <v>38</v>
       </c>
       <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10092,9 +10103,12 @@
         <v>31</v>
       </c>
       <c r="L17" s="4" t="n">
+        <v>-5.54</v>
+      </c>
+      <c r="M17" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10147,9 +10161,12 @@
         <v>9</v>
       </c>
       <c r="L18" s="4" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="M18" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10202,9 +10219,12 @@
         <v>19</v>
       </c>
       <c r="L19" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M19" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10257,9 +10277,12 @@
         <v>39</v>
       </c>
       <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10312,9 +10335,12 @@
         <v>75</v>
       </c>
       <c r="L21" s="4" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="M21" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10367,9 +10393,12 @@
         <v>10</v>
       </c>
       <c r="L22" s="4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="M22" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10422,9 +10451,12 @@
         <v>39</v>
       </c>
       <c r="L23" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M23" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10477,9 +10509,12 @@
         <v>16</v>
       </c>
       <c r="L24" s="4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M24" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10532,9 +10567,12 @@
         <v>15</v>
       </c>
       <c r="L25" s="4" t="n">
+        <v>-7.28</v>
+      </c>
+      <c r="M25" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10587,9 +10625,12 @@
         <v>43</v>
       </c>
       <c r="L26" s="4" t="n">
+        <v>-5.17</v>
+      </c>
+      <c r="M26" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10642,9 +10683,12 @@
         <v>35</v>
       </c>
       <c r="L27" s="4" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="M27" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10697,9 +10741,12 @@
         <v>38</v>
       </c>
       <c r="L28" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M28" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10752,9 +10799,12 @@
         <v>14</v>
       </c>
       <c r="L29" s="6" t="n">
+        <v>-4.91</v>
+      </c>
+      <c r="M29" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -10807,9 +10857,12 @@
         <v>15</v>
       </c>
       <c r="L30" s="6" t="n">
+        <v>-5.73</v>
+      </c>
+      <c r="M30" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="M30" s="7" t="inlineStr">
+      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -10862,9 +10915,12 @@
         <v>14</v>
       </c>
       <c r="L31" s="8" t="n">
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="M31" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="M31" s="9" t="inlineStr">
+      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10912,12 +10968,11 @@
       <c r="K32" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="L32" s="10" t="inlineStr"/>
-      <c r="M32" s="11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="L32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="10" t="inlineStr"/>
+      <c r="N32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -10961,12 +11016,11 @@
       <c r="K33" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L33" s="12" t="inlineStr"/>
-      <c r="M33" s="13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="L33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="12" t="inlineStr"/>
+      <c r="N33" s="13" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -11008,12 +11062,11 @@
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr"/>
-      <c r="L34" s="10" t="inlineStr"/>
-      <c r="M34" s="11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="L34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="10" t="inlineStr"/>
+      <c r="N34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -11057,12 +11110,11 @@
       <c r="K35" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L35" s="12" t="inlineStr"/>
-      <c r="M35" s="13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="L35" s="12" t="n">
+        <v>-7.69</v>
+      </c>
+      <c r="M35" s="12" t="inlineStr"/>
+      <c r="N35" s="13" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -11106,12 +11158,11 @@
       <c r="K36" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="L36" s="10" t="inlineStr"/>
-      <c r="M36" s="11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="L36" s="10" t="n">
+        <v>-4.53</v>
+      </c>
+      <c r="M36" s="10" t="inlineStr"/>
+      <c r="N36" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ae_master.xlsx
+++ b/ae_master.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>109</v>
+        <v>451</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>13</v>
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>8</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>11</v>
@@ -731,16 +731,16 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>S64602</t>
+          <t>S70645</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>McLean</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -751,10 +751,10 @@
         <v>3</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4</v>
+        <v>249</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -800,13 +800,13 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -835,16 +835,16 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>S59656</t>
+          <t>S64602</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>McLean</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -881,22 +881,22 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>S40835</t>
+          <t>S64603</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Gallia Academy</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5</v>
+        <v>135</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Partial / Issues</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>26</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -956,13 +956,13 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>88</v>
+        <v>856</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -991,16 +991,16 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>S70645</t>
+          <t>S44882</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>Monroe Landfill</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
         <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>On Track</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>S44882</t>
+          <t>S59656</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Monroe Landfill</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>4</v>
+        <v>367</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1089,22 +1089,22 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>S64603</t>
+          <t>S40835</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Gallia Academy</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1127,192 +1127,192 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Partial / Issues</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>91</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>S65784</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Washington Solar</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>401</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Below Expected</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>S63839</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>S65785</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Harding Solar</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="2" t="n">
+      <c r="C15" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L15" s="5" t="n">
         <v>41</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>S65784</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Washington Solar</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>S65788</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Gray Fox Solar</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>S63839</t>
+          <t>S65786</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
@@ -1323,10 +1323,10 @@
         <v>1</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1349,22 +1349,22 @@
         </is>
       </c>
       <c r="L16" s="5" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>S65786</t>
+          <t>S65788</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -1392,16 +1392,16 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -1427,7 +1427,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>5</v>
@@ -1459,12 +1459,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>S40836</t>
+          <t>S63837</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande Elementary</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5</v>
+        <v>170</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>3</v>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -1531,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>3</v>
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>S51957</t>
+          <t>S66001</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>WCPS - William Perry Elementary School</t>
+          <t>Sheridan Solar</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
@@ -1632,17 +1632,17 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1657,26 +1657,26 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L22" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>S63837</t>
+          <t>S51957</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>WCPS - William Perry Elementary School</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -1687,14 +1687,14 @@
         <v>1</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -1713,22 +1713,22 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>S40834</t>
+          <t>S54613</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Green Elementary</t>
+          <t>Warbler</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>1</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4</v>
+        <v>132</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
@@ -1761,26 +1761,26 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L24" s="5" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>S66001</t>
+          <t>S44566</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Sheridan Solar</t>
+          <t>RIT</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -1791,10 +1791,10 @@
         <v>1</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -1817,18 +1817,18 @@
         </is>
       </c>
       <c r="L25" s="5" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>S54613</t>
+          <t>S63838</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Warbler</t>
+          <t>Bulloch 1A</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -1843,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>2</v>
@@ -1865,26 +1865,26 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L26" s="5" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>S44566</t>
+          <t>S40836</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>RIT</t>
+          <t>Rio Grande Elementary</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -1917,26 +1917,26 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L27" s="5" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>S63838</t>
+          <t>S40834</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Bulloch 1A</t>
+          <t>Green Elementary</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
@@ -1944,287 +1944,307 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G28" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S68112</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Wallace Solar</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>S54553</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Butler Maple</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>All Communicating</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="n">
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
+          <t>S54553</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Butler Maple</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>All Communicating</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>S65216</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Green Solar</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>All Communicating</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t>S66000</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Auburn Solar</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="6" t="n">
+      <c r="E32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>All Communicating</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>Below Expected</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>S68113</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Marble Solar</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Clean</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>All Communicating</t>
         </is>
       </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>S68113</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Marble Solar</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Clean</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>All Communicating</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L31" s="9" t="n">
+      <c r="L33" s="9" t="n">
         <v>14</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>S51958</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>WCPS - Westwood Hills Elementary School</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr"/>
-      <c r="D32" s="10" t="inlineStr"/>
-      <c r="E32" s="10" t="inlineStr"/>
-      <c r="F32" s="10" t="inlineStr"/>
-      <c r="G32" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
-        </is>
-      </c>
-      <c r="K32" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L32" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>S51959</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>WCPS - Waynesboro High School</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr"/>
-      <c r="D33" s="12" t="inlineStr"/>
-      <c r="E33" s="12" t="inlineStr"/>
-      <c r="F33" s="12" t="inlineStr"/>
-      <c r="G33" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J33" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K33" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L33" s="13" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>S55935</t>
+          <t>S51958</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Manuel Lawrence Dairy</t>
+          <t>WCPS - Westwood Hills Elementary School</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr"/>
@@ -2232,11 +2252,11 @@
       <c r="E34" s="10" t="inlineStr"/>
       <c r="F34" s="10" t="inlineStr"/>
       <c r="G34" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
@@ -2246,7 +2266,7 @@
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
@@ -2254,17 +2274,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L34" s="11" t="inlineStr"/>
+      <c r="L34" s="11" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>S65216</t>
+          <t>S51959</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Green Solar</t>
+          <t>WCPS - Waynesboro High School</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr"/>
@@ -2272,16 +2294,16 @@
       <c r="E35" s="12" t="inlineStr"/>
       <c r="F35" s="12" t="inlineStr"/>
       <c r="G35" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>All Communicating</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
@@ -2291,53 +2313,11 @@
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L35" s="13" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>S68112</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Wallace Solar</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr"/>
-      <c r="D36" s="10" t="inlineStr"/>
-      <c r="E36" s="10" t="inlineStr"/>
-      <c r="F36" s="10" t="inlineStr"/>
-      <c r="G36" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K36" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L36" s="11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2351,7 +2331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -2421,7 +2401,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>13</v>
@@ -2449,7 +2429,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -2457,7 +2437,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>8</v>
@@ -2485,7 +2465,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -2493,7 +2473,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>11</v>
@@ -2517,11 +2497,11 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>McLean</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -2532,7 +2512,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -2557,7 +2537,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -2565,10 +2545,10 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -2589,11 +2569,11 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>McLean</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -2601,10 +2581,10 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -2618,18 +2598,18 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Gallia Academy</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -2637,10 +2617,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -2649,12 +2629,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Partial / Issues</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2645,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -2673,10 +2653,10 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -2697,11 +2677,11 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>Monroe Landfill</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -2712,7 +2692,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -2726,18 +2706,18 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>On Track</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Monroe Landfill</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -2745,10 +2725,10 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -2769,11 +2749,11 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Gallia Academy</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -2781,10 +2761,10 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -2793,118 +2773,118 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Partial / Issues</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>Washington Solar</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Below Expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Harding Solar</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="2" t="n">
+      <c r="B15" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Washington Solar</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Gray Fox Solar</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -2913,11 +2893,11 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -2928,7 +2908,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
@@ -2942,18 +2922,18 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
@@ -2961,10 +2941,10 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
@@ -2978,7 +2958,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3001,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande Elementary</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
@@ -3097,7 +3077,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -3105,10 +3085,10 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
@@ -3129,11 +3109,11 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>WCPS - William Perry Elementary School</t>
+          <t>Sheridan Solar</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
@@ -3141,14 +3121,14 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -3165,11 +3145,11 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>WCPS - William Perry Elementary School</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -3180,11 +3160,11 @@
         <v>1</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -3194,18 +3174,18 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Green Elementary</t>
+          <t>Warbler</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
@@ -3216,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
@@ -3237,11 +3217,11 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Sheridan Solar</t>
+          <t>RIT</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
@@ -3252,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
@@ -3266,14 +3246,14 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Warbler</t>
+          <t>Bulloch 1A</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
@@ -3309,11 +3289,11 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>RIT</t>
+          <t>Rio Grande Elementary</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -3321,10 +3301,10 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
@@ -3345,11 +3325,11 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Bulloch 1A</t>
+          <t>Green Elementary</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
@@ -3357,186 +3337,202 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Wallace Solar</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Butler Maple</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>All Communicating</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>On Track</t>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
+          <t>Butler Maple</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>All Communicating</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Green Solar</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>All Communicating</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t>Auburn Solar</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="D32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>All Communicating</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Below Expected</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Marble Solar</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n">
+      <c r="B33" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="D33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>Clean</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>All Communicating</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>WCPS - Westwood Hills Elementary School</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr"/>
-      <c r="C32" s="10" t="inlineStr"/>
-      <c r="D32" s="10" t="inlineStr"/>
-      <c r="E32" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>WCPS - Waynesboro High School</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr"/>
-      <c r="C33" s="12" t="inlineStr"/>
-      <c r="D33" s="12" t="inlineStr"/>
-      <c r="E33" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -3545,18 +3541,18 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Manuel Lawrence Dairy</t>
+          <t>WCPS - Westwood Hills Elementary School</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr"/>
       <c r="C34" s="10" t="inlineStr"/>
       <c r="D34" s="10" t="inlineStr"/>
       <c r="E34" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -3566,61 +3562,33 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Green Solar</t>
+          <t>WCPS - Waynesboro High School</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr"/>
       <c r="C35" s="12" t="inlineStr"/>
       <c r="D35" s="12" t="inlineStr"/>
       <c r="E35" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>All Communicating</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>Wallace Solar</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr"/>
-      <c r="C36" s="10" t="inlineStr"/>
-      <c r="D36" s="10" t="inlineStr"/>
-      <c r="E36" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -3637,14 +3605,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3686,7 +3654,7 @@
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>84</v>
+        <v>835</v>
       </c>
       <c r="D2" s="10" t="n">
         <v>0</v>
@@ -3698,64 +3666,64 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Solectria XGI 1500 Series - Fault Alert</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>81</v>
+        <v>385</v>
       </c>
       <c r="D3" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>0.1851851851851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Solectria XGI 1500 Series - Fault Alert</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>78</v>
+        <v>313</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0</v>
+        <v>0.07987220447284345</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Sungrow Inverter Fault Alert</t>
+          <t>Gamechange Tracker Alert</t>
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.2380952380952381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3770,13 +3738,13 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0</v>
+        <v>0.03067484662576687</v>
       </c>
     </row>
     <row r="7">
@@ -3787,17 +3755,17 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Gamechange Tracker Alert</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>0.2941176470588235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3812,13 +3780,13 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.03703703703703703</v>
       </c>
     </row>
     <row r="9">
@@ -3833,112 +3801,112 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>0.3125</v>
+        <v>0.04545454545454546</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Sungrow Inverter Fault Alert</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>5</v>
+        <v>0.0505050505050505</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Elk Solar</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Device heartbeat</t>
+          <t>Solectria XGI 1000 Series - Fault Alert</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Warbler</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Inverter / irradiance check</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Solectria XGI 1000 Series - Fault Alert</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>2.222222222222222</v>
+        <v>0.078125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Warbler</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Inverter / irradiance check</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>0</v>
@@ -3950,28 +3918,28 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Rio Grande Elementary</t>
+          <t>McLean</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Power Meter Check 2.0</t>
+          <t>Sungrow Inverter Fault Alert</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Auburn Solar</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -3980,28 +3948,28 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0</v>
+        <v>1.323529411764706</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Marble Solar</t>
+          <t>Warbler</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Sungrow Inverter Fault Alert</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D17" s="12" t="n">
         <v>0</v>
@@ -4013,16 +3981,16 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Gallia Academy</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Sungrow Inverter Fault Alert</t>
+          <t>Power Meter Check 2.0</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>0</v>
@@ -4034,16 +4002,16 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Green Elementary</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Power Meter Check 2.0</t>
+          <t>Sungrow Inverter Fault Alert</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>0</v>
@@ -4055,7 +4023,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Gallia Academy</t>
+          <t>Rio Grande Elementary</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -4064,7 +4032,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>0</v>
@@ -4076,16 +4044,16 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Power Meter Check 2.0</t>
+          <t>Sungrow Inverter Fault Alert</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>0</v>
@@ -4097,106 +4065,106 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>McLean</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>WCPS - William Perry Elementary School</t>
+          <t>Longleaf Pine Solar, LLC</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Sungrow Inverter Fault Alert</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>RRH 1 &amp; 2</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>.Chint / Solectria / Canadian String Inv Faults</t>
+          <t>Power Meter Check 2.0</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Auburn Solar</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Sungrow Inverter Fault Alert</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Solar FlexRack Tracker Alert (revG)</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="E26" s="11" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27">
@@ -4207,107 +4175,107 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Solar FlexRack Tracker Alert (revG)</t>
+          <t>Power Meter Check 2.0</t>
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Phoenix Contact - Quint UPS Alerts (QUINT4 EIP)</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>2.5</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Upson</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Solar FlexRack Tracker Alert</t>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>5</v>
+        <v>0.3571428571428572</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -4316,61 +4284,61 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>.Chint / Solectria / Canadian String Inv Faults</t>
         </is>
       </c>
       <c r="C33" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="E33" s="13" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Harding Solar</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>RIT</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
@@ -4379,19 +4347,19 @@
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D35" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>2.5</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Monroe Landfill</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -4400,82 +4368,82 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D36" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>2.5</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>McLean</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Transformer Monitor</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D38" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts (QUINT4 EIP)</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Elk Solar</t>
+          <t>Monroe Landfill</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -4484,91 +4452,91 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>2.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>McLean</t>
+          <t>Marble Solar</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Sungrow 3150U/3425U/3600U inverter alerts</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>RRH 1 &amp; 2</t>
+          <t>Elk Solar</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Power Meter Check 2.0</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Green Solar</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Elk Solar</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Sungrow Inverter Fault Alert</t>
+          <t>Device heartbeat</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>0</v>
@@ -4580,70 +4548,70 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>Longleaf Pine Solar, LLC</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts (QUINT4 EIP)</t>
+          <t>Transformer Monitor</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D45" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="E45" s="13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>Bulloch 1A</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Site Controller Health</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Longleaf Pine Solar, LLC</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Weather Station Alert</t>
+          <t>Phoenix Contact - Quint UPS Alerts (QUINT4 EIP)</t>
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Butler Maple</t>
+          <t>Bulloch 1A</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -4652,55 +4620,55 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D48" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>5</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Gateway heartbeat</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D49" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>5</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>RIT</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Device heartbeat</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D50" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>5</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="51">
@@ -4711,95 +4679,95 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>.Chint / Solectria / Canadian String Inv Faults</t>
+          <t>Power Meter Check 2.0</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Monroe Landfill</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Power Meter Check 2.0</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>RRH 1 &amp; 2</t>
+          <t>Monroe Landfill</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Report run-time alert</t>
+          <t>Gateway heartbeat</t>
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>McLean</t>
+          <t>Monroe Landfill</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Solar FlexRack Tracker Alert (revG)</t>
+          <t>.Chint / Solectria / Canadian String Inv Faults</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D54" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>5</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Marble Solar</t>
+          <t>Green Elementary</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Sungrow 3150U/3425U/3600U inverter alerts</t>
+          <t>Power Meter Check 2.0</t>
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D55" s="12" t="n">
         <v>0</v>
@@ -4811,37 +4779,37 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>McLean</t>
+          <t>Upson</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D56" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>5</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>Gray Fox Solar</t>
+          <t>Marble Solar</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D57" s="12" t="n">
         <v>0</v>
@@ -4858,32 +4826,32 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>SEL Recloser Open Alarm</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Gray Fox Solar</t>
+          <t>Warbler</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>SEL Recloser Open Alarm</t>
+          <t>Gateway heartbeat</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D59" s="12" t="n">
         <v>0</v>
@@ -4895,58 +4863,58 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Gray Fox Solar</t>
+          <t>Warbler</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Solar FlexRack/OMCO Tracker Alert (revM)</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>Green Elementary</t>
+          <t>Auburn Solar</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Harding Solar</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts</t>
+          <t>Gateway heartbeat</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D62" s="10" t="n">
         <v>0</v>
@@ -4958,7 +4926,7 @@
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>Harding Solar</t>
+          <t>Auburn Solar</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
@@ -4967,40 +4935,40 @@
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>Harding Solar</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Solar FlexRack/OMCO Tracker Alert (revM)</t>
+          <t>Transformer Monitor</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Sheridan Solar</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
@@ -5009,28 +4977,28 @@
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D65" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>5</v>
+        <v>1.666666666666667</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Gray Fox Solar</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Gateway heartbeat</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" s="10" t="n">
         <v>0</v>
@@ -5042,159 +5010,159 @@
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>Gallia Academy</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Gateway heartbeat</t>
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Gallia Academy</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>RRH 1 &amp; 2</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Solar FlexRack/OMCO Tracker Alert (revM)</t>
+          <t>.Chint / Solectria / Canadian String Inv Faults</t>
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>RRH 1 &amp; 2</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Solar FlexRack Tracker Alert (revM)v2</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>Rio Grande Elementary</t>
+          <t>WCPS - Kate Collins Middle School</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Performance Index Alert</t>
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>Sheridan Solar</t>
+          <t>Butler Maple</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>WCPS - William Perry Elementary School</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Performance Index Alert</t>
+          <t>Solar FlexRack/OMCO Tracker Alert (revM)</t>
         </is>
       </c>
       <c r="C73" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>WCPS - Kate Collins Middle School</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Performance Index Alert</t>
+          <t>Device heartbeat</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
@@ -5210,54 +5178,54 @@
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>Rio Grande Elementary</t>
+          <t>Butler Maple</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Weather Station Alert</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Warbler</t>
+          <t>Monroe Landfill</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Inverter stopped alert</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sheridan Solar</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>SEL Recloser Open Alarm</t>
+          <t>Phoenix Contact - Quint UPS Alerts (QUINT4 EIP)</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
@@ -5273,12 +5241,12 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Rio Grande Elementary</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>Power Meter Check 2.0</t>
+          <t>Weather Station Alert</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
@@ -5294,12 +5262,12 @@
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>RRH 1 &amp; 2</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts</t>
+          <t>Inverter / irradiance check</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
@@ -5315,22 +5283,274 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
+          <t>Longleaf Pine Solar, LLC</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Power Meter Check 2.0</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>Longleaf Pine Solar, LLC</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>SEL Recloser Open Alarm</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Longleaf Pine Solar, LLC</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Device heartbeat</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>Longleaf Pine Solar, LLC</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>Gateway heartbeat</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>WCPS - William Perry Elementary School</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Rule Tool Alert</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>Washington Solar</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>SEL Recloser Open Alarm</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>Washington Solar</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Power Meter Check 2.0</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>Warbler</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>Wallace Solar</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>Device communication</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>Whitetail</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>Data Comparison Alert</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
           <t>Whitehall Solar</t>
         </is>
       </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>Rule Tool Alert</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="11" t="n">
-        <v>5</v>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>SEL Recloser Open Alarm</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>Whitetail</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>SEL Recloser Open Alarm</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>Whitetail</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5348,7 +5568,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
@@ -5378,52 +5598,52 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 4</t>
+          <t>GameChange Tracker Control 2.1</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>TKR</t>
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>53</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>GameChange Tracker Control 2.1</t>
+          <t>INVERTER 20</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>TKR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D3" s="13" t="n">
-        <v>23</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>INVERTER A20</t>
+          <t>INVERTER 4</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -5432,18 +5652,18 @@
         </is>
       </c>
       <c r="D4" s="11" t="n">
-        <v>22</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 20</t>
+          <t>INVERTER A20</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -5452,7 +5672,7 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -5472,18 +5692,18 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 3</t>
+          <t>INVERTER 25</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5492,18 +5712,18 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 62</t>
+          <t>INVERTER 16</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -5512,18 +5732,18 @@
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 13</t>
+          <t>INVERTER 22</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -5532,7 +5752,7 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -5543,7 +5763,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 25</t>
+          <t>INVERTER 72</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -5552,18 +5772,18 @@
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 26</t>
+          <t>INVERTER 2</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -5572,7 +5792,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -5592,18 +5812,18 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 14</t>
+          <t>INVERTER 63</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -5612,7 +5832,7 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -5623,7 +5843,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 15</t>
+          <t>INVERTER 8</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -5632,27 +5852,27 @@
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Rio Grande Elementary</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 12</t>
+          <t>Elkor Production Meter</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>MTR</t>
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -5663,7 +5883,7 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 71</t>
+          <t>INVERTER 41</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -5672,18 +5892,18 @@
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 7</t>
+          <t>INVERTER 6</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -5692,18 +5912,18 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 9</t>
+          <t>Inverter 18</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -5712,18 +5932,18 @@
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Auburn Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>INVERTER MODULE 1</t>
+          <t>INVERTER 13</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -5732,18 +5952,18 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Inverter 24</t>
+          <t>INVERTER 23</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -5752,78 +5972,78 @@
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Marble Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>DC ZONES</t>
+          <t>INVERTER 26</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>HCB</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>METER - PRODUCTION</t>
+          <t>INVERTER 42</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>MTR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Rio Grande Elementary</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Elkor Production Meter</t>
+          <t>INVERTER 62</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>MTR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 76</t>
+          <t>INVERTER 17</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -5832,18 +6052,18 @@
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 17</t>
+          <t>INVERTER 64</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -5852,38 +6072,38 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Green Elementary</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Elkor MKII Production Meter</t>
+          <t>GameChange Tracker Control 2.2</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>MTR</t>
+          <t>TKR</t>
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 48</t>
+          <t>INVERTER 3</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -5892,18 +6112,18 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 46</t>
+          <t>INVERTER 22</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -5912,38 +6132,38 @@
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 2</t>
+          <t>TRACKER CONTROL (ST1)</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>TKR</t>
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 4</t>
+          <t>INVERTER 45</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -5952,18 +6172,18 @@
         </is>
       </c>
       <c r="D30" s="11" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>INVERTER B11</t>
+          <t>INVERTER 48</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -5972,18 +6192,18 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>INVERTER B15</t>
+          <t>INVERTER 70</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -5992,7 +6212,7 @@
         </is>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -6003,7 +6223,7 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 8</t>
+          <t>INVERTER 10</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -6012,18 +6232,18 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 11</t>
+          <t>INVERTER 73</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -6032,7 +6252,7 @@
         </is>
       </c>
       <c r="D34" s="11" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
@@ -6043,7 +6263,7 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 1</t>
+          <t>INVERTER 14</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -6052,18 +6272,18 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 10</t>
+          <t>INVERTER 30</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -6072,18 +6292,18 @@
         </is>
       </c>
       <c r="D36" s="11" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 64</t>
+          <t>Inverter 13</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
@@ -6092,7 +6312,7 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
@@ -6112,7 +6332,7 @@
         </is>
       </c>
       <c r="D38" s="11" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
@@ -6123,7 +6343,7 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 41</t>
+          <t>INVERTER 66</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -6132,7 +6352,7 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
@@ -6143,7 +6363,7 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 72</t>
+          <t>INVERTER 49</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -6152,27 +6372,27 @@
         </is>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Gallia Academy</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Tracker Controller 2</t>
+          <t>Elkor Production Meter (Main)</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>TKR</t>
+          <t>MTR</t>
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -6183,7 +6403,7 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 35</t>
+          <t>INVERTER 53</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -6192,18 +6412,18 @@
         </is>
       </c>
       <c r="D42" s="11" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Inverter 14</t>
+          <t>INVERTER 44</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -6212,18 +6432,18 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Inverter 13</t>
+          <t>INVERTER 9</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -6232,18 +6452,18 @@
         </is>
       </c>
       <c r="D44" s="11" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 22</t>
+          <t>INVERTER 18</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
@@ -6252,38 +6472,38 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Inverter 16</t>
+          <t>METER - PRODUCTION</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>MTR</t>
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Inverter 22</t>
+          <t>INVERTER 27</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -6292,7 +6512,7 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
@@ -6303,7 +6523,7 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Inverter 18</t>
+          <t>Inverter 22</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -6312,78 +6532,78 @@
         </is>
       </c>
       <c r="D48" s="11" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>PYRANOMETER - BPOA</t>
+          <t>INVERTER 1</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>ALSOENERGY SMART UPS</t>
+          <t>INVERTER 12</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>DA</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D50" s="11" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Gallia Academy</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Elkor Production Meter (Main)</t>
+          <t>INVERTER 4</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>MTR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Inverter 23</t>
+          <t>INVERTER 46</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -6392,38 +6612,38 @@
         </is>
       </c>
       <c r="D52" s="11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>DIGITAL I/O - XFMR ALARMS</t>
+          <t>INVERTER 51</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>DA</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>INVERTER B15</t>
+          <t>INVERTER 19</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -6432,18 +6652,18 @@
         </is>
       </c>
       <c r="D54" s="11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 7</t>
+          <t>INVERTER 43</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -6452,18 +6672,18 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 9</t>
+          <t>Inverter 24</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -6472,7 +6692,7 @@
         </is>
       </c>
       <c r="D56" s="11" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -6492,18 +6712,18 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>SunGrow SG125HV - Inverter 22</t>
+          <t>Inverter 21</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -6512,18 +6732,18 @@
         </is>
       </c>
       <c r="D58" s="11" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>INVERTER B8</t>
+          <t>INVERTER 31</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -6532,38 +6752,38 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>GameChange Tracker Control 2.2</t>
+          <t>INVERTER 25</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>TKR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D60" s="11" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 36</t>
+          <t>INVERTER 28</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -6572,7 +6792,7 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
@@ -6583,7 +6803,7 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 5</t>
+          <t>INVERTER 9</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -6592,18 +6812,18 @@
         </is>
       </c>
       <c r="D62" s="11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 19</t>
+          <t>Inverter 14</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -6612,7 +6832,7 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64">
@@ -6623,7 +6843,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 16</t>
+          <t>INVERTER 7</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -6632,18 +6852,18 @@
         </is>
       </c>
       <c r="D64" s="11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 20</t>
+          <t>INVERTER 61</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -6652,7 +6872,7 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66">
@@ -6663,7 +6883,7 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 45</t>
+          <t>INVERTER 74</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -6672,7 +6892,7 @@
         </is>
       </c>
       <c r="D66" s="11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67">
@@ -6683,7 +6903,7 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 43</t>
+          <t>INVERTER 35</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -6692,18 +6912,18 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 17</t>
+          <t>INVERTER 24</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -6712,27 +6932,27 @@
         </is>
       </c>
       <c r="D68" s="11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>TRACKER CONTROL (ST1)</t>
+          <t>ALSOENERGY SMART UPS</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>TKR</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70">
@@ -6743,7 +6963,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 22</t>
+          <t>INVERTER 55</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -6752,18 +6972,18 @@
         </is>
       </c>
       <c r="D70" s="11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 24</t>
+          <t>INVERTER 15</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -6772,7 +6992,7 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72">
@@ -6783,7 +7003,7 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 49</t>
+          <t>INVERTER 71</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -6792,7 +7012,7 @@
         </is>
       </c>
       <c r="D72" s="11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73">
@@ -6803,7 +7023,7 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 34</t>
+          <t>INVERTER 65</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -6812,27 +7032,27 @@
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 52</t>
+          <t>ALSOENERGY SMART UPS</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75">
@@ -6843,7 +7063,7 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 50</t>
+          <t>INVERTER 68</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -6852,18 +7072,18 @@
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>INVERTER B8</t>
+          <t>INVERTER 47</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -6872,18 +7092,18 @@
         </is>
       </c>
       <c r="D76" s="11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 27</t>
+          <t>INVERTER 11</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -6892,7 +7112,7 @@
         </is>
       </c>
       <c r="D77" s="13" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78">
@@ -6903,7 +7123,7 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 31</t>
+          <t>INVERTER 29</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -6912,7 +7132,7 @@
         </is>
       </c>
       <c r="D78" s="11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79">
@@ -6923,7 +7143,7 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 67</t>
+          <t>INVERTER 56</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -6932,7 +7152,7 @@
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80">
@@ -6943,7 +7163,7 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 33</t>
+          <t>INVERTER 75</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -6952,18 +7172,18 @@
         </is>
       </c>
       <c r="D80" s="11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Longleaf Pine Solar, LLC</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 63</t>
+          <t>INVERTER B5</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
@@ -6972,58 +7192,58 @@
         </is>
       </c>
       <c r="D81" s="13" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>ALSOENERGY SMART UPS</t>
+          <t>INVERTER 50</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>DA</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D82" s="11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Gallia Academy</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 6</t>
+          <t>Elkor Production Meter (Remote)</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>MTR</t>
         </is>
       </c>
       <c r="D83" s="13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>Gray Fox Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 2.6</t>
+          <t>INVERTER 20</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
@@ -7032,18 +7252,18 @@
         </is>
       </c>
       <c r="D84" s="11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>INVERTER B3</t>
+          <t>INVERTER 5</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -7052,18 +7272,18 @@
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>INVERTER B2</t>
+          <t>INVERTER B15</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
@@ -7072,18 +7292,18 @@
         </is>
       </c>
       <c r="D86" s="11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>INVERTER B18</t>
+          <t>INVERTER 54</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -7092,18 +7312,18 @@
         </is>
       </c>
       <c r="D87" s="13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>INVERTER B17</t>
+          <t>INVERTER 67</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
@@ -7112,18 +7332,18 @@
         </is>
       </c>
       <c r="D88" s="11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>INVERTER B16</t>
+          <t>Inverter 16</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -7132,27 +7352,27 @@
         </is>
       </c>
       <c r="D89" s="13" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>INVERTER B14</t>
+          <t>TRACKER CONTROL (ST2)</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>TKR</t>
         </is>
       </c>
       <c r="D90" s="11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
@@ -7163,7 +7383,7 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>INVERTER B13</t>
+          <t>INVERTER B3</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -7172,18 +7392,18 @@
         </is>
       </c>
       <c r="D91" s="13" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>INVERTER B12</t>
+          <t>Inverter 17</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
@@ -7192,38 +7412,38 @@
         </is>
       </c>
       <c r="D92" s="11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>Harding Solar</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>ALSOENERGY SMART UPS</t>
+          <t>Inverter 23</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>DA</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D93" s="13" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>INVERTER B11</t>
+          <t>INVERTER 76</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
@@ -7232,18 +7452,18 @@
         </is>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>INVERTER B10</t>
+          <t>Inverter 20</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -7252,118 +7472,118 @@
         </is>
       </c>
       <c r="D95" s="13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>Harding Solar</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>TRACKER  CONTROL</t>
+          <t>Inverter 19</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>TKR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D96" s="11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>Gray Fox Solar</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>ALSOENERGY SMART UPS</t>
+          <t>PowerManager 2200 (RMA16217/SO101810)</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>DA</t>
+          <t>GTW</t>
         </is>
       </c>
       <c r="D97" s="13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>CPS SCH125kTL Inv - 8</t>
+          <t>GameChange Tracker Control 2.3</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>TKR</t>
         </is>
       </c>
       <c r="D98" s="11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>RRH 1 &amp; 2</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Cell Modem Reporting (RV50)</t>
+          <t>Elkor Production Meter Site 1</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>DA</t>
+          <t>MTR</t>
         </is>
       </c>
       <c r="D99" s="13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>PowerLogger 1000 (SO95895)</t>
+          <t>INVERTER 77</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>GTW</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D100" s="11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Inverter 20</t>
+          <t>INVERTER 33</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -7372,7 +7592,7 @@
         </is>
       </c>
       <c r="D101" s="13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -9095,7 +9315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9198,10 +9418,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>109</v>
+        <v>451</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>13</v>
@@ -9233,7 +9453,7 @@
         <v>55</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.27</v>
+        <v>2997.62</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>95</v>
@@ -9256,10 +9476,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>8</v>
@@ -9294,7 +9514,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
@@ -9314,10 +9534,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>11</v>
@@ -9352,7 +9572,7 @@
         <v>-1.2</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -9363,22 +9583,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>S64602</t>
+          <t>S70645</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>McLean</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4</v>
+        <v>249</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>3</v>
@@ -9404,13 +9624,13 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-8.49</v>
+        <v>4392.82</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
@@ -9430,13 +9650,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>3</v>
@@ -9465,10 +9685,10 @@
         <v>52</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-11.97</v>
+        <v>4329.73</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -9479,22 +9699,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>S59656</t>
+          <t>S64602</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>McLean</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>3</v>
@@ -9511,7 +9731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9520,13 +9740,13 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-11.93</v>
+        <v>4934.78</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
@@ -9537,22 +9757,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>S40835</t>
+          <t>S64603</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Gallia Academy</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>5</v>
+        <v>135</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>3</v>
@@ -9564,27 +9784,27 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Partial / Issues</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.02</v>
+        <v>4932.99</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -9604,13 +9824,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>88</v>
+        <v>856</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>3</v>
@@ -9639,10 +9859,10 @@
         <v>103</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-14.72</v>
+        <v>9358.77</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
@@ -9653,22 +9873,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>S70645</t>
+          <t>S44882</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>Monroe Landfill</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>3</v>
@@ -9685,7 +9905,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>On Track</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9694,13 +9914,13 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-7.22</v>
+        <v>1543.82</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -9711,22 +9931,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>S44882</t>
+          <t>S59656</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Monroe Landfill</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4</v>
+        <v>367</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>3</v>
@@ -9752,13 +9972,13 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-0.86</v>
+        <v>8436.879999999999</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
@@ -9769,22 +9989,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>S64603</t>
+          <t>S40835</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Gallia Academy</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>3</v>
@@ -9796,27 +10016,27 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Partial / Issues</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-12.76</v>
+        <v>211.75</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -9827,22 +10047,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>S65785</t>
+          <t>S65784</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Harding Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3</v>
+        <v>401</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>3</v>
@@ -9859,7 +10079,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9868,155 +10088,155 @@
         </is>
       </c>
       <c r="K13" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>4436.72</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>S63839</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>S65785</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Harding Solar</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="L13" s="2" t="n">
-        <v>-6.75</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>S65784</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Washington Solar</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n">
+      <c r="L15" s="4" t="n">
+        <v>2964.47</v>
+      </c>
+      <c r="M15" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="L14" s="2" t="n">
-        <v>-6.31</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>S65788</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Gray Fox Solar</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>-7.93</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>S63839</t>
+          <t>S65786</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>3</v>
@@ -10033,7 +10253,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -10042,13 +10262,13 @@
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0</v>
+        <v>1981.03</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
@@ -10059,22 +10279,22 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>S65786</t>
+          <t>S65788</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>3</v>
@@ -10091,22 +10311,22 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-5.54</v>
+        <v>2685.48</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
@@ -10126,7 +10346,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>1</v>
@@ -10161,7 +10381,7 @@
         <v>9</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.24</v>
+        <v>215.83</v>
       </c>
       <c r="M18" s="4" t="n">
         <v>55</v>
@@ -10175,16 +10395,16 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>S40836</t>
+          <t>S63837</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande Elementary</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>5</v>
+        <v>170</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>2</v>
@@ -10216,10 +10436,10 @@
         </is>
       </c>
       <c r="K19" s="4" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.05</v>
+        <v>2490</v>
       </c>
       <c r="M19" s="4" t="n">
         <v>54</v>
@@ -10242,7 +10462,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>1</v>
@@ -10277,7 +10497,7 @@
         <v>39</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0</v>
+        <v>2364</v>
       </c>
       <c r="M20" s="4" t="n">
         <v>54</v>
@@ -10300,13 +10520,13 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>3</v>
@@ -10335,10 +10555,10 @@
         <v>75</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.19</v>
+        <v>3962.42</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
@@ -10349,29 +10569,29 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>S51957</t>
+          <t>S66001</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>WCPS - William Perry Elementary School</t>
+          <t>Sheridan Solar</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -10386,17 +10606,17 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K22" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.01</v>
+        <v>1843.26</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
@@ -10407,29 +10627,29 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>S63837</t>
+          <t>S51957</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>WCPS - William Perry Elementary School</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -10439,7 +10659,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -10448,13 +10668,13 @@
         </is>
       </c>
       <c r="K23" s="4" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-6</v>
+        <v>69.12</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
@@ -10465,22 +10685,22 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>S40834</t>
+          <t>S54613</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Green Elementary</t>
+          <t>Warbler</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4</v>
+        <v>132</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>3</v>
@@ -10502,17 +10722,17 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K24" s="4" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>1202.68</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
@@ -10523,22 +10743,22 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>S66001</t>
+          <t>S44566</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Sheridan Solar</t>
+          <t>RIT</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>3</v>
@@ -10555,7 +10775,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -10564,13 +10784,13 @@
         </is>
       </c>
       <c r="K25" s="4" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-7.28</v>
+        <v>1592.17</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
@@ -10581,16 +10801,16 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>S54613</t>
+          <t>S63838</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Warbler</t>
+          <t>Bulloch 1A</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>1</v>
@@ -10618,14 +10838,14 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K26" s="4" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-5.17</v>
+        <v>2982</v>
       </c>
       <c r="M26" s="4" t="n">
         <v>46</v>
@@ -10639,22 +10859,22 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>S44566</t>
+          <t>S40836</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>RIT</t>
+          <t>Rio Grande Elementary</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>3</v>
@@ -10676,17 +10896,17 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K27" s="4" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.39</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
@@ -10697,22 +10917,22 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>S63838</t>
+          <t>S40834</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Bulloch 1A</t>
+          <t>Green Elementary</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>3</v>
@@ -10738,13 +10958,13 @@
         </is>
       </c>
       <c r="K28" s="4" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-6</v>
+        <v>106.22</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
@@ -10753,297 +10973,317 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>S54553</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Butler Maple</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="6" t="n">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S68112</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Wallace Solar</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>All Communicating</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="n">
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="L29" s="6" t="n">
-        <v>-4.91</v>
-      </c>
-      <c r="M29" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="L29" s="4" t="n">
+        <v>437.95</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
+          <t>S54553</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Butler Maple</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>All Communicating</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>3157.28</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>S65216</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Green Solar</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>All Communicating</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>2595.23</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t>S66000</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Auburn Solar</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C32" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>All Communicating</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Below Expected</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>713.39</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>S68113</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Marble Solar</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Clean</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>All Communicating</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>2841.94</v>
+      </c>
+      <c r="M33" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>All Communicating</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="L30" s="6" t="n">
-        <v>-5.73</v>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>S68113</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Marble Solar</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>Clean</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>All Communicating</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="L31" s="8" t="n">
-        <v>-8.449999999999999</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N31" s="9" t="inlineStr">
+      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>S51958</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>WCPS - Westwood Hills Elementary School</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr"/>
-      <c r="D32" s="10" t="inlineStr"/>
-      <c r="E32" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K32" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>S51959</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>WCPS - Waynesboro High School</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr"/>
-      <c r="D33" s="12" t="inlineStr"/>
-      <c r="E33" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J33" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="12" t="inlineStr"/>
-      <c r="N33" s="13" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>S55935</t>
+          <t>S51958</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Manuel Lawrence Dairy</t>
+          <t>WCPS - Westwood Hills Elementary School</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr"/>
       <c r="D34" s="10" t="inlineStr"/>
       <c r="E34" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -11053,7 +11293,7 @@
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
@@ -11061,9 +11301,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K34" s="10" t="inlineStr"/>
+      <c r="K34" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="L34" s="10" t="n">
-        <v>0</v>
+        <v>84.59</v>
       </c>
       <c r="M34" s="10" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr"/>
@@ -11071,30 +11313,30 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>S65216</t>
+          <t>S51959</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Green Solar</t>
+          <t>WCPS - Waynesboro High School</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr"/>
       <c r="D35" s="12" t="inlineStr"/>
       <c r="E35" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>All Communicating</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
@@ -11104,65 +11346,17 @@
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K35" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>-7.69</v>
+        <v>84.23</v>
       </c>
       <c r="M35" s="12" t="inlineStr"/>
       <c r="N35" s="13" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>S68112</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Wallace Solar</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr"/>
-      <c r="D36" s="10" t="inlineStr"/>
-      <c r="E36" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K36" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="L36" s="10" t="n">
-        <v>-4.53</v>
-      </c>
-      <c r="M36" s="10" t="inlineStr"/>
-      <c r="N36" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ae_master.xlsx
+++ b/ae_master.xlsx
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>451</v>
+        <v>396</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>13</v>
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>8</v>
@@ -679,16 +679,16 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>S54681</t>
+          <t>S70645</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>13</v>
+        <v>235</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Partial / Issues</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>S70645</t>
+          <t>S66930</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>Elk Solar</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -748,13 +748,13 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>249</v>
+        <v>15</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -777,22 +777,22 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>S66930</t>
+          <t>S64602</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Elk Solar</t>
+          <t>McLean</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -800,13 +800,13 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -829,22 +829,22 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>S64602</t>
+          <t>S65787</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>McLean</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>72</v>
+        <v>782</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -881,22 +881,22 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>S64603</t>
+          <t>S40835</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Gallia Academy</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -919,36 +919,36 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Partial / Issues</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>91</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>S65787</t>
+          <t>S59656</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -956,13 +956,13 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>856</v>
+        <v>346</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>On Track</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -985,22 +985,22 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>S44882</t>
+          <t>S65784</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Monroe Landfill</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>28</v>
+        <v>362</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Partial / Issues</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>S59656</t>
+          <t>S64603</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>367</v>
+        <v>128</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1075,140 +1075,140 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>S54681</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Eagle</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>S44882</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Monroe Landfill</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
           <t>Partial / Issues</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>On Track</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L11" s="3" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>S40835</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Gallia Academy</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Partial / Issues</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>S65784</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Washington Solar</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>401</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>58</v>
+      <c r="L13" s="5" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>S63839</t>
+          <t>S65788</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
@@ -1216,13 +1216,13 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -1241,26 +1241,26 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L14" s="5" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>S65785</t>
+          <t>S51960</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Harding Solar</t>
+          <t>WCPS - Kate Collins Middle School</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
@@ -1271,48 +1271,48 @@
         <v>1</v>
       </c>
       <c r="F15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="n">
         <v>9</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>S65786</t>
+          <t>S65785</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>Harding Solar</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
@@ -1320,13 +1320,13 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
@@ -1340,31 +1340,31 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L16" s="5" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>S65788</t>
+          <t>S65786</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Gray Fox Solar</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -1392,31 +1392,31 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>S51960</t>
+          <t>S63839</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>WCPS - Kate Collins Middle School</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>5</v>
@@ -1449,26 +1449,26 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L18" s="5" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>S63837</t>
+          <t>S44485</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>RRH 1 &amp; 2</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>170</v>
+        <v>25</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -1505,22 +1505,22 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>S63840</t>
+          <t>S63837</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Upson</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>3</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1563,16 +1563,16 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>S44485</t>
+          <t>S63840</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>RRH 1 &amp; 2</t>
+          <t>Upson</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1609,22 +1609,22 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>75</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>S66001</t>
+          <t>S63838</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Sheridan Solar</t>
+          <t>Bulloch 1A</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
@@ -1635,10 +1635,10 @@
         <v>1</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
@@ -1652,31 +1652,31 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L22" s="5" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>S51957</t>
+          <t>S66001</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>WCPS - William Perry Elementary School</t>
+          <t>Sheridan Solar</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -1684,17 +1684,17 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -1709,26 +1709,26 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>S54613</t>
+          <t>S40836</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Warbler</t>
+          <t>Rio Grande Elementary</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
@@ -1761,26 +1761,26 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L24" s="5" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>S44566</t>
+          <t>S40834</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>RIT</t>
+          <t>Green Elementary</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -1788,13 +1788,13 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1813,26 +1813,26 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L25" s="5" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>S63838</t>
+          <t>S44566</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Bulloch 1A</t>
+          <t>RIT</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
@@ -1865,26 +1865,26 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L26" s="5" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>S40836</t>
+          <t>S51957</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande Elementary</t>
+          <t>WCPS - William Perry Elementary School</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
@@ -1895,14 +1895,14 @@
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="L27" s="5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>S40834</t>
+          <t>S68112</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Green Elementary</t>
+          <t>Wallace Solar</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
@@ -1969,63 +1969,63 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L28" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>S68112</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Wallace Solar</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>S54613</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Warbler</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>131</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n">
-        <v>14</v>
+      <c r="L29" s="7" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="30">
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>3</v>
@@ -2155,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>0</v>
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>13</v>
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>8</v>
@@ -2461,11 +2461,11 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Partial / Issues</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2497,11 +2497,11 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>Elk Solar</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -2533,11 +2533,11 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Elk Solar</t>
+          <t>McLean</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -2569,11 +2569,11 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>McLean</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -2598,18 +2598,18 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Gallia Academy</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -2629,23 +2629,23 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Partial / Issues</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -2670,18 +2670,18 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>On Track</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Monroe Landfill</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -2701,23 +2701,23 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Partial / Issues</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Below Expected</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -2737,95 +2737,95 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Eagle</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Monroe Landfill</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
           <t>Partial / Issues</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>On Track</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Gallia Academy</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Partial / Issues</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Washington Solar</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -2857,11 +2857,11 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Harding Solar</t>
+          <t>WCPS - Kate Collins Middle School</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
@@ -2893,11 +2893,11 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>Harding Solar</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
@@ -2922,18 +2922,18 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Gray Fox Solar</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
@@ -2958,18 +2958,18 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>WCPS - Kate Collins Middle School</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>5</v>
@@ -3001,11 +3001,11 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>RRH 1 &amp; 2</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
@@ -3037,11 +3037,11 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Upson</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -3066,18 +3066,18 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>RRH 1 &amp; 2</t>
+          <t>Upson</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
@@ -3102,18 +3102,18 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Sheridan Solar</t>
+          <t>Bulloch 1A</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
@@ -3138,18 +3138,18 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>WCPS - William Perry Elementary School</t>
+          <t>Sheridan Solar</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -3157,14 +3157,14 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -3181,11 +3181,11 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Warbler</t>
+          <t>Rio Grande Elementary</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
@@ -3217,11 +3217,11 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>RIT</t>
+          <t>Green Elementary</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
@@ -3253,11 +3253,11 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Bulloch 1A</t>
+          <t>RIT</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
@@ -3289,11 +3289,11 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande Elementary</t>
+          <t>WCPS - William Perry Elementary School</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -3304,11 +3304,11 @@
         <v>0</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -3318,18 +3318,18 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Green Elementary</t>
+          <t>Wallace Solar</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
@@ -3359,36 +3359,36 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Wallace Solar</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Warbler</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>3</v>
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>835</v>
+        <v>762</v>
       </c>
       <c r="D2" s="10" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>385</v>
+        <v>346</v>
       </c>
       <c r="D3" s="12" t="n">
         <v>0</v>
@@ -3696,13 +3696,13 @@
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>313</v>
+        <v>275</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.07987220447284345</v>
+        <v>0.03636363636363636</v>
       </c>
     </row>
     <row r="5">
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="D5" s="12" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -3738,19 +3738,19 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.03067484662576687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D7" s="12" t="n">
         <v>0</v>
@@ -3780,13 +3780,13 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.04032258064516129</v>
       </c>
     </row>
     <row r="9">
@@ -3801,13 +3801,13 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.04901960784313725</v>
       </c>
     </row>
     <row r="10">
@@ -3834,43 +3834,43 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Warbler</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Solectria XGI 1000 Series - Fault Alert</t>
+          <t>Inverter / irradiance check</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.2173913043478261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Warbler</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Inverter / irradiance check</t>
+          <t>Solectria XGI 1000 Series - Fault Alert</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0</v>
+        <v>0.1176470588235294</v>
       </c>
     </row>
     <row r="13">
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>0.078125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3939,28 +3939,28 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Warbler</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Sungrow Inverter Fault Alert</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1.323529411764706</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Warbler</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D17" s="12" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>0</v>
@@ -4002,37 +4002,37 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Sungrow Inverter Fault Alert</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Rio Grande Elementary</t>
+          <t>McLean</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Power Meter Check 2.0</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>0</v>
@@ -4065,16 +4065,16 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>McLean</t>
+          <t>Rio Grande Elementary</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Power Meter Check 2.0</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" s="10" t="n">
         <v>0</v>
@@ -4158,28 +4158,28 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.5</v>
+        <v>0.2777777777777778</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Power Meter Check 2.0</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D27" s="12" t="n">
         <v>0</v>
@@ -4191,37 +4191,37 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts (QUINT4 EIP)</t>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Transformer Monitor</t>
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D29" s="12" t="n">
         <v>0</v>
@@ -4233,37 +4233,37 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts</t>
+          <t>Phoenix Contact - Quint UPS Alerts (QUINT4 EIP)</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.3571428571428572</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts</t>
+          <t>Power Meter Check 2.0</t>
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D31" s="12" t="n">
         <v>0</v>
@@ -4275,16 +4275,16 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Transformer Monitor</t>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>0</v>
@@ -4305,40 +4305,40 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Harding Solar</t>
+          <t>Elk Solar</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts</t>
+          <t>Device heartbeat</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
@@ -4347,19 +4347,19 @@
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -4368,19 +4368,19 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>McLean</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
@@ -4389,19 +4389,19 @@
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>McLean</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -4413,73 +4413,73 @@
         <v>8</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Harding Solar</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
         </is>
       </c>
       <c r="C39" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Monroe Landfill</t>
+          <t>Green Solar</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Marble Solar</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Sungrow 3150U/3425U/3600U inverter alerts</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="42">
@@ -4494,49 +4494,49 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Green Solar</t>
+          <t>Bulloch 1A</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Elk Solar</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Device heartbeat</t>
+          <t>Site Controller Health</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>0</v>
@@ -4553,28 +4553,28 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Transformer Monitor</t>
+          <t>Phoenix Contact - Quint UPS Alerts (QUINT4 EIP)</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Site Controller Health</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
@@ -4590,12 +4590,12 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Monroe Landfill</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts (QUINT4 EIP)</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C47" s="12" t="n">
@@ -4611,54 +4611,54 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Bulloch 1A</t>
+          <t>Marble Solar</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Sungrow 3150U/3425U/3600U inverter alerts</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
         <v>7</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Monroe Landfill</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Power Meter Check 2.0</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
         <v>7</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>RIT</t>
+          <t>Longleaf Pine Solar, LLC</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Transformer Monitor</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
@@ -4674,16 +4674,16 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Monroe Landfill</t>
+          <t>RIT</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Power Meter Check 2.0</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D51" s="12" t="n">
         <v>0</v>
@@ -4695,37 +4695,37 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Monroe Landfill</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Gateway heartbeat</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
         <v>6</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>Monroe Landfill</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Gateway heartbeat</t>
+          <t>SEL Recloser Open Alarm</t>
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53" s="12" t="n">
         <v>0</v>
@@ -4737,37 +4737,37 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Monroe Landfill</t>
+          <t>Green Elementary</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>.Chint / Solectria / Canadian String Inv Faults</t>
+          <t>Power Meter Check 2.0</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Green Elementary</t>
+          <t>Upson</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Power Meter Check 2.0</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55" s="12" t="n">
         <v>0</v>
@@ -4779,7 +4779,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Upson</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -4788,13 +4788,13 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -4821,12 +4821,12 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Gray Fox Solar</t>
+          <t>Warbler</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>SEL Recloser Open Alarm</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
@@ -4842,12 +4842,12 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Warbler</t>
+          <t>Monroe Landfill</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Gateway heartbeat</t>
+          <t>.Chint / Solectria / Canadian String Inv Faults</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
@@ -4868,17 +4868,17 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Gateway heartbeat</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
@@ -4926,16 +4926,16 @@
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>Auburn Solar</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Transformer Monitor</t>
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D63" s="12" t="n">
         <v>0</v>
@@ -4947,12 +4947,12 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>Sheridan Solar</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Transformer Monitor</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
@@ -4968,22 +4968,22 @@
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>Sheridan Solar</t>
+          <t>Auburn Solar</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C65" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5010,33 +5010,33 @@
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Gateway heartbeat</t>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
         </is>
       </c>
       <c r="C67" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Gray Fox Solar</t>
+          <t>RRH 1 &amp; 2</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts</t>
+          <t>.Chint / Solectria / Canadian String Inv Faults</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>.Chint / Solectria / Canadian String Inv Faults</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C69" s="12" t="n">
@@ -5073,54 +5073,54 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>RRH 1 &amp; 2</t>
+          <t>WCPS - Kate Collins Middle School</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Performance Index Alert</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>WCPS - Kate Collins Middle School</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Performance Index Alert</t>
+          <t>Gateway heartbeat</t>
         </is>
       </c>
       <c r="C71" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>Butler Maple</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts</t>
+          <t>Solar FlexRack/OMCO Tracker Alert (revM)</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
@@ -5136,12 +5136,12 @@
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>Gray Fox Solar</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Solar FlexRack/OMCO Tracker Alert (revM)</t>
+          <t>Device heartbeat</t>
         </is>
       </c>
       <c r="C73" s="12" t="n">
@@ -5157,54 +5157,54 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Butler Maple</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Device heartbeat</t>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>Butler Maple</t>
+          <t>Monroe Landfill</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>Inverter stopped alert</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Monroe Landfill</t>
+          <t>Sheridan Solar</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>Inverter stopped alert</t>
+          <t>Phoenix Contact - Quint UPS Alerts (QUINT4 EIP)</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
@@ -5220,12 +5220,12 @@
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>Sheridan Solar</t>
+          <t>Rio Grande Elementary</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts (QUINT4 EIP)</t>
+          <t>Weather Station Alert</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
@@ -5241,12 +5241,12 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Rio Grande Elementary</t>
+          <t>RRH 1 &amp; 2</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>Weather Station Alert</t>
+          <t>Inverter / irradiance check</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
@@ -5262,12 +5262,12 @@
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>RRH 1 &amp; 2</t>
+          <t>Longleaf Pine Solar, LLC</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Inverter / irradiance check</t>
+          <t>Power Meter Check 2.0</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Power Meter Check 2.0</t>
+          <t>SEL Recloser Open Alarm</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>SEL Recloser Open Alarm</t>
+          <t>Device heartbeat</t>
         </is>
       </c>
       <c r="C81" s="12" t="n">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Device heartbeat</t>
+          <t>Gateway heartbeat</t>
         </is>
       </c>
       <c r="C82" s="10" t="n">
@@ -5346,12 +5346,12 @@
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>WCPS - William Perry Elementary School</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Gateway heartbeat</t>
+          <t>Rule Tool Alert</t>
         </is>
       </c>
       <c r="C83" s="12" t="n">
@@ -5367,22 +5367,22 @@
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>WCPS - William Perry Elementary School</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>Rule Tool Alert</t>
+          <t>SEL Recloser Open Alarm</t>
         </is>
       </c>
       <c r="C84" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>SEL Recloser Open Alarm</t>
+          <t>Power Meter Check 2.0</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
@@ -5409,12 +5409,12 @@
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Warbler</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>Power Meter Check 2.0</t>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
@@ -5430,12 +5430,12 @@
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t>Warbler</t>
+          <t>Wallace Solar</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Contact - Quint UPS Alerts</t>
+          <t>Device communication</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
@@ -5451,12 +5451,12 @@
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>Wallace Solar</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Device communication</t>
+          <t>Data Comparison Alert</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
@@ -5472,12 +5472,12 @@
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Data Comparison Alert</t>
+          <t>SEL Recloser Open Alarm</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
@@ -5493,7 +5493,7 @@
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>SEL Recloser Open Alarm</t>
+          <t>Phoenix Contact - Quint UPS Alerts</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
@@ -5529,27 +5529,6 @@
         <v>0</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>Whitetail</t>
-        </is>
-      </c>
-      <c r="B92" s="10" t="inlineStr">
-        <is>
-          <t>Phoenix Contact - Quint UPS Alerts</t>
-        </is>
-      </c>
-      <c r="C92" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5612,7 +5591,7 @@
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3">
@@ -5632,18 +5611,18 @@
         </is>
       </c>
       <c r="D3" s="13" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 4</t>
+          <t>INVERTER A20</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -5652,18 +5631,18 @@
         </is>
       </c>
       <c r="D4" s="11" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>INVERTER A20</t>
+          <t>INVERTER 4</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -5672,7 +5651,7 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -5683,7 +5662,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 1</t>
+          <t>INVERTER 25</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -5692,7 +5671,7 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -5703,7 +5682,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 25</t>
+          <t>INVERTER 1</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5712,7 +5691,7 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -5732,18 +5711,18 @@
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 22</t>
+          <t>INVERTER 2</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -5752,7 +5731,7 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -5763,7 +5742,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 72</t>
+          <t>INVERTER 63</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -5772,18 +5751,18 @@
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 2</t>
+          <t>INVERTER 72</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -5792,7 +5771,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -5803,7 +5782,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 21</t>
+          <t>INVERTER 22</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -5812,7 +5791,7 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -5823,7 +5802,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 63</t>
+          <t>INVERTER 41</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -5832,18 +5811,18 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 8</t>
+          <t>INVERTER 21</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -5852,47 +5831,47 @@
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Rio Grande Elementary</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Elkor Production Meter</t>
+          <t>INVERTER 8</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>MTR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Rio Grande Elementary</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 41</t>
+          <t>Elkor Production Meter</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>MTR</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -5912,18 +5891,18 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Inverter 18</t>
+          <t>INVERTER 62</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -5932,7 +5911,7 @@
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -5943,7 +5922,7 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 13</t>
+          <t>INVERTER 17</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -5952,38 +5931,38 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 23</t>
+          <t>GameChange Tracker Control 2.2</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>TKR</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 26</t>
+          <t>INVERTER 22</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -5992,18 +5971,18 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 42</t>
+          <t>INVERTER 13</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -6012,7 +5991,7 @@
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -6023,7 +6002,7 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 62</t>
+          <t>INVERTER 45</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -6032,18 +6011,18 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 17</t>
+          <t>INVERTER 42</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -6052,7 +6031,7 @@
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -6072,38 +6051,38 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>GameChange Tracker Control 2.2</t>
+          <t>INVERTER 3</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>TKR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 3</t>
+          <t>INVERTER 26</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -6112,18 +6091,18 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 22</t>
+          <t>INVERTER 23</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -6132,38 +6111,38 @@
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>TRACKER CONTROL (ST1)</t>
+          <t>INVERTER 30</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>TKR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 45</t>
+          <t>Inverter 18</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -6172,7 +6151,7 @@
         </is>
       </c>
       <c r="D30" s="11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -6183,7 +6162,7 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 48</t>
+          <t>INVERTER 70</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -6192,7 +6171,7 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
@@ -6203,7 +6182,7 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 70</t>
+          <t>INVERTER 69</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -6212,18 +6191,18 @@
         </is>
       </c>
       <c r="D32" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 10</t>
+          <t>INVERTER 49</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -6232,18 +6211,18 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 73</t>
+          <t>INVERTER 9</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -6252,18 +6231,18 @@
         </is>
       </c>
       <c r="D34" s="11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 14</t>
+          <t>INVERTER 48</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -6272,18 +6251,18 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 30</t>
+          <t>INVERTER 12</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -6292,18 +6271,18 @@
         </is>
       </c>
       <c r="D36" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Inverter 13</t>
+          <t>INVERTER 66</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
@@ -6312,47 +6291,47 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 69</t>
+          <t>TRACKER CONTROL (ST1)</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>TKR</t>
         </is>
       </c>
       <c r="D38" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Gallia Academy</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 66</t>
+          <t>Elkor Production Meter (Main)</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>MTR</t>
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
@@ -6363,7 +6342,7 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 49</t>
+          <t>INVERTER 73</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -6372,27 +6351,27 @@
         </is>
       </c>
       <c r="D40" s="11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Gallia Academy</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Elkor Production Meter (Main)</t>
+          <t>Inverter 13</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>MTR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -6412,18 +6391,18 @@
         </is>
       </c>
       <c r="D42" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 44</t>
+          <t>INVERTER 14</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -6432,18 +6411,18 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 9</t>
+          <t>INVERTER 44</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -6452,7 +6431,7 @@
         </is>
       </c>
       <c r="D44" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -6472,38 +6451,38 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>METER - PRODUCTION</t>
+          <t>INVERTER 10</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>MTR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 27</t>
+          <t>Inverter 22</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -6512,18 +6491,18 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Inverter 22</t>
+          <t>INVERTER 4</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -6532,18 +6511,18 @@
         </is>
       </c>
       <c r="D48" s="11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 1</t>
+          <t>Inverter 21</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -6552,18 +6531,18 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 12</t>
+          <t>INVERTER 74</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -6572,18 +6551,18 @@
         </is>
       </c>
       <c r="D50" s="11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 4</t>
+          <t>INVERTER 28</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -6592,7 +6571,7 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
@@ -6603,7 +6582,7 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 46</t>
+          <t>INVERTER 65</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -6612,7 +6591,7 @@
         </is>
       </c>
       <c r="D52" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
@@ -6623,7 +6602,7 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 51</t>
+          <t>INVERTER 35</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -6632,18 +6611,18 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 19</t>
+          <t>INVERTER 27</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -6652,7 +6631,7 @@
         </is>
       </c>
       <c r="D54" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55">
@@ -6663,7 +6642,7 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 43</t>
+          <t>INVERTER 55</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -6672,18 +6651,18 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Inverter 24</t>
+          <t>INVERTER 51</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -6692,13 +6671,13 @@
         </is>
       </c>
       <c r="D56" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
@@ -6712,18 +6691,18 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Inverter 21</t>
+          <t>INVERTER 1</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -6732,18 +6711,18 @@
         </is>
       </c>
       <c r="D58" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 31</t>
+          <t>INVERTER 9</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -6752,7 +6731,7 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
@@ -6763,7 +6742,7 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 25</t>
+          <t>INVERTER 43</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -6772,7 +6751,7 @@
         </is>
       </c>
       <c r="D60" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61">
@@ -6783,7 +6762,7 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 28</t>
+          <t>INVERTER 56</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -6792,7 +6771,7 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
@@ -6803,7 +6782,7 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 9</t>
+          <t>INVERTER 7</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -6812,18 +6791,18 @@
         </is>
       </c>
       <c r="D62" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Inverter 14</t>
+          <t>INVERTER 24</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -6832,27 +6811,27 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 7</t>
+          <t>METER - PRODUCTION</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>MTR</t>
         </is>
       </c>
       <c r="D64" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
@@ -6863,7 +6842,7 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 61</t>
+          <t>INVERTER 50</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -6872,18 +6851,18 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 74</t>
+          <t>Inverter 24</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -6892,18 +6871,18 @@
         </is>
       </c>
       <c r="D66" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 35</t>
+          <t>INVERTER 19</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -6912,7 +6891,7 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
@@ -6923,7 +6902,7 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 24</t>
+          <t>INVERTER 71</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -6932,27 +6911,27 @@
         </is>
       </c>
       <c r="D68" s="11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>ALSOENERGY SMART UPS</t>
+          <t>INVERTER 68</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>DA</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -6963,7 +6942,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 55</t>
+          <t>INVERTER 75</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -6972,18 +6951,18 @@
         </is>
       </c>
       <c r="D70" s="11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 15</t>
+          <t>INVERTER 47</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -6992,7 +6971,7 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
@@ -7003,7 +6982,7 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 71</t>
+          <t>INVERTER 46</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -7012,18 +6991,18 @@
         </is>
       </c>
       <c r="D72" s="11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Longleaf Pine Solar, LLC</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 65</t>
+          <t>INVERTER B5</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -7032,27 +7011,27 @@
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>ALSOENERGY SMART UPS</t>
+          <t>INVERTER 54</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>DA</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75">
@@ -7063,7 +7042,7 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 68</t>
+          <t>INVERTER 25</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -7072,18 +7051,18 @@
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 47</t>
+          <t>Inverter 14</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -7092,38 +7071,38 @@
         </is>
       </c>
       <c r="D76" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 11</t>
+          <t>ALSOENERGY SMART UPS</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="D77" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 29</t>
+          <t>INVERTER 20</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -7132,7 +7111,7 @@
         </is>
       </c>
       <c r="D78" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79">
@@ -7143,7 +7122,7 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 56</t>
+          <t>INVERTER 31</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -7152,7 +7131,7 @@
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80">
@@ -7163,7 +7142,7 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 75</t>
+          <t>INVERTER 29</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -7172,18 +7151,18 @@
         </is>
       </c>
       <c r="D80" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>INVERTER B5</t>
+          <t>INVERTER 11</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
@@ -7192,118 +7171,118 @@
         </is>
       </c>
       <c r="D81" s="13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 50</t>
+          <t>ALSOENERGY SMART UPS</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="D82" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>Gallia Academy</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Elkor Production Meter (Remote)</t>
+          <t>INVERTER 5</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>MTR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D83" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 20</t>
+          <t>TRACKER CONTROL (ST2)</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>TKR</t>
         </is>
       </c>
       <c r="D84" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Gallia Academy</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 5</t>
+          <t>Elkor Production Meter (Remote)</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>MTR</t>
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>RRH 1 &amp; 2</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>INVERTER B15</t>
+          <t>Elkor Production Meter Site 2</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>MTR</t>
         </is>
       </c>
       <c r="D86" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 54</t>
+          <t>INVERTER B2</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -7312,78 +7291,78 @@
         </is>
       </c>
       <c r="D87" s="13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>RRH 1 &amp; 2</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 67</t>
+          <t>Elkor Production Meter Site 1</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>MTR</t>
         </is>
       </c>
       <c r="D88" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Inverter 16</t>
+          <t>PowerManager 2200 (RMA16217/SO101810)</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>GTW</t>
         </is>
       </c>
       <c r="D89" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>TRACKER CONTROL (ST2)</t>
+          <t>INVERTER 77</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>TKR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D90" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>INVERTER B3</t>
+          <t>INVERTER 61</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -7392,18 +7371,18 @@
         </is>
       </c>
       <c r="D91" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Inverter 17</t>
+          <t>INVERTER 76</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
@@ -7412,18 +7391,18 @@
         </is>
       </c>
       <c r="D92" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Longleaf Pine Solar, LLC</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Inverter 23</t>
+          <t>INVERTER B3</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -7432,7 +7411,7 @@
         </is>
       </c>
       <c r="D93" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
@@ -7443,7 +7422,7 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 76</t>
+          <t>INVERTER 33</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
@@ -7452,18 +7431,18 @@
         </is>
       </c>
       <c r="D94" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Inverter 20</t>
+          <t>INVERTER B15</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -7483,7 +7462,7 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Inverter 19</t>
+          <t>Inverter 20</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -7498,17 +7477,17 @@
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>PowerManager 2200 (RMA16217/SO101810)</t>
+          <t>Inverter 23</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>GTW</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D97" s="13" t="n">
@@ -7518,41 +7497,41 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>GameChange Tracker Control 2.3</t>
+          <t>INVERTER 19</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>TKR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D98" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>RRH 1 &amp; 2</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Elkor Production Meter Site 1</t>
+          <t>Inverter 16</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>MTR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="D99" s="13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100">
@@ -7563,7 +7542,7 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>INVERTER 77</t>
+          <t>INVERTER 67</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
@@ -7572,18 +7551,18 @@
         </is>
       </c>
       <c r="D100" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>INVERTER 33</t>
+          <t>Inverter 17</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -7592,7 +7571,7 @@
         </is>
       </c>
       <c r="D101" s="13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9418,10 +9397,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>451</v>
+        <v>396</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>13</v>
@@ -9453,7 +9432,7 @@
         <v>55</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2997.62</v>
+        <v>574.63</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>95</v>
@@ -9476,10 +9455,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>8</v>
@@ -9514,7 +9493,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
@@ -9525,22 +9504,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>S54681</t>
+          <t>S70645</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>13</v>
+        <v>235</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>3</v>
@@ -9552,7 +9531,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Partial / Issues</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -9566,13 +9545,13 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-1.2</v>
+        <v>168.89</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -9583,22 +9562,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>S70645</t>
+          <t>S66930</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Williams Solar, LLC</t>
+          <t>Elk Solar</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>249</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>3</v>
@@ -9624,13 +9603,13 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>4392.82</v>
+        <v>220.76</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
@@ -9641,22 +9620,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>S66930</t>
+          <t>S64602</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Elk Solar</t>
+          <t>McLean</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>3</v>
@@ -9682,13 +9661,13 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>4329.73</v>
+        <v>305.56</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -9699,22 +9678,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>S64602</t>
+          <t>S65787</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>McLean</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>72</v>
+        <v>782</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>3</v>
@@ -9731,7 +9710,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9740,13 +9719,13 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>4934.78</v>
+        <v>-20.48</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
@@ -9757,22 +9736,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>S64603</t>
+          <t>S40835</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Gallia Academy</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>3</v>
@@ -9784,27 +9763,27 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Partial / Issues</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>4932.99</v>
+        <v>53.09</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -9815,22 +9794,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>S65787</t>
+          <t>S59656</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>856</v>
+        <v>346</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>3</v>
@@ -9847,7 +9826,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>On Track</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9856,13 +9835,13 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>9358.77</v>
+        <v>301.06</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
@@ -9873,22 +9852,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>S44882</t>
+          <t>S65784</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Monroe Landfill</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>28</v>
+        <v>362</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>3</v>
@@ -9900,12 +9879,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Partial / Issues</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9914,13 +9893,13 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1543.82</v>
+        <v>311.21</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -9931,22 +9910,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>S59656</t>
+          <t>S64603</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>367</v>
+        <v>128</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>3</v>
@@ -9958,169 +9937,169 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>632.33</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>S54681</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Eagle</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>166.22</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>S44882</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Monroe Landfill</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
           <t>Partial / Issues</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>On Track</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K11" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>8436.879999999999</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>S40835</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Gallia Academy</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Partial / Issues</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>211.75</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>S65784</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Washington Solar</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>401</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Below Expected</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="M13" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="L13" s="2" t="n">
-        <v>4436.72</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>S63839</t>
+          <t>S65788</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>3</v>
@@ -10142,17 +10121,17 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K14" s="4" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2496</v>
+        <v>178.43</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
@@ -10163,22 +10142,22 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>S65785</t>
+          <t>S51960</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Harding Solar</t>
+          <t>WCPS - Kate Collins Middle School</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>3</v>
@@ -10204,13 +10183,13 @@
         </is>
       </c>
       <c r="K15" s="4" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2964.47</v>
+        <v>33.74</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
@@ -10221,22 +10200,22 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>S65786</t>
+          <t>S65785</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>Harding Solar</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>3</v>
@@ -10253,22 +10232,22 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1981.03</v>
+        <v>153.46</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
@@ -10279,22 +10258,22 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>S65788</t>
+          <t>S65786</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Gray Fox Solar</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>3</v>
@@ -10311,22 +10290,22 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2685.48</v>
+        <v>32.37</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
@@ -10337,19 +10316,19 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>S51960</t>
+          <t>S63839</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>WCPS - Kate Collins Middle School</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>5</v>
@@ -10374,17 +10353,17 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K18" s="4" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>215.83</v>
+        <v>120</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
@@ -10395,22 +10374,22 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>S63837</t>
+          <t>S44485</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>RRH 1 &amp; 2</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>170</v>
+        <v>25</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>3</v>
@@ -10436,13 +10415,13 @@
         </is>
       </c>
       <c r="K19" s="4" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2490</v>
+        <v>184</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
@@ -10453,16 +10432,16 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>S63840</t>
+          <t>S63837</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Upson</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>1</v>
@@ -10485,7 +10464,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -10497,10 +10476,10 @@
         <v>39</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2364</v>
+        <v>108</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
@@ -10511,22 +10490,22 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>S44485</t>
+          <t>S63840</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>RRH 1 &amp; 2</t>
+          <t>Upson</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>3</v>
@@ -10543,7 +10522,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -10552,13 +10531,13 @@
         </is>
       </c>
       <c r="K21" s="4" t="n">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3962.42</v>
+        <v>180</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
@@ -10569,22 +10548,22 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>S66001</t>
+          <t>S63838</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Sheridan Solar</t>
+          <t>Bulloch 1A</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>3</v>
@@ -10601,22 +10580,22 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Below Expected</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K22" s="4" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1843.26</v>
+        <v>276</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
@@ -10627,29 +10606,29 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>S51957</t>
+          <t>S66001</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>WCPS - William Perry Elementary School</t>
+          <t>Sheridan Solar</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -10664,17 +10643,17 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K23" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>69.12</v>
+        <v>1508.25</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
@@ -10685,22 +10664,22 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>S54613</t>
+          <t>S40836</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Warbler</t>
+          <t>Rio Grande Elementary</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>3</v>
@@ -10722,17 +10701,17 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K24" s="4" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1202.68</v>
+        <v>16.36</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
@@ -10743,22 +10722,22 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>S44566</t>
+          <t>S40834</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>RIT</t>
+          <t>Green Elementary</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>3</v>
@@ -10780,17 +10759,17 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K25" s="4" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1592.17</v>
+        <v>14.14</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
@@ -10801,22 +10780,22 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>S63838</t>
+          <t>S44566</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Bulloch 1A</t>
+          <t>RIT</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>3</v>
@@ -10838,17 +10817,17 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K26" s="4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2982</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
@@ -10859,29 +10838,29 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>S40836</t>
+          <t>S51957</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande Elementary</t>
+          <t>WCPS - William Perry Elementary School</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -10891,7 +10870,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Below Expected</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -10900,13 +10879,13 @@
         </is>
       </c>
       <c r="K27" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>80.51000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
@@ -10917,22 +10896,22 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>S40834</t>
+          <t>S68112</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Green Elementary</t>
+          <t>Wallace Solar</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>3</v>
@@ -10954,17 +10933,17 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K28" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>106.22</v>
+        <v>661.89</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
@@ -10973,60 +10952,60 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>S68112</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Wallace Solar</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" s="4" t="n">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>S54613</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Warbler</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>131</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K29" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>437.95</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="K29" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>86.12</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -11042,10 +11021,10 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>3</v>
@@ -11077,10 +11056,10 @@
         <v>14</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>3157.28</v>
+        <v>3913.66</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
@@ -11135,7 +11114,7 @@
         <v>16</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>2595.23</v>
+        <v>541.6799999999999</v>
       </c>
       <c r="M31" s="6" t="n">
         <v>33</v>
@@ -11158,7 +11137,7 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>0</v>
@@ -11193,7 +11172,7 @@
         <v>15</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>713.39</v>
+        <v>918.41</v>
       </c>
       <c r="M32" s="6" t="n">
         <v>25</v>
@@ -11216,7 +11195,7 @@
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>0</v>
@@ -11251,7 +11230,7 @@
         <v>14</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>2841.94</v>
+        <v>2840.55</v>
       </c>
       <c r="M33" s="8" t="n">
         <v>5</v>
@@ -11305,7 +11284,7 @@
         <v>7</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>84.59</v>
+        <v>16.59</v>
       </c>
       <c r="M34" s="10" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr"/>
@@ -11353,7 +11332,7 @@
         <v>7</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>84.23</v>
+        <v>12.48</v>
       </c>
       <c r="M35" s="12" t="inlineStr"/>
       <c r="N35" s="13" t="inlineStr"/>
